--- a/research/traditional_assets/database/data/india/india_banks_regional.xlsx
+++ b/research/traditional_assets/database/data/india/india_banks_regional.xlsx
@@ -588,10 +588,13 @@
         </is>
       </c>
       <c r="D2">
-        <v>0.2145</v>
+        <v>0.20105</v>
+      </c>
+      <c r="E2">
+        <v>0.00342</v>
       </c>
       <c r="F2">
-        <v>0.124</v>
+        <v>0.242</v>
       </c>
       <c r="G2">
         <v>0</v>
@@ -600,34 +603,34 @@
         <v>0</v>
       </c>
       <c r="I2">
-        <v>0.0005833977725316943</v>
+        <v>0.0036175914943207</v>
       </c>
       <c r="J2">
-        <v>0.0005089544877933999</v>
+        <v>0.002862667548699841</v>
       </c>
       <c r="K2">
-        <v>-150.59</v>
+        <v>766.23</v>
       </c>
       <c r="L2">
-        <v>-0.1796159351145038</v>
+        <v>0.3434622797973912</v>
       </c>
       <c r="M2">
-        <v>21.7</v>
+        <v>3.87</v>
       </c>
       <c r="N2">
-        <v>0.001998839383583726</v>
+        <v>0.0003495019371618998</v>
       </c>
       <c r="O2">
-        <v>-0.1440998738296035</v>
+        <v>0.005050702791589993</v>
       </c>
       <c r="P2">
-        <v>21.7</v>
+        <v>3.87</v>
       </c>
       <c r="Q2">
-        <v>0.001998839383583726</v>
+        <v>0.0003495019371618998</v>
       </c>
       <c r="R2">
-        <v>-0.1440998738296035</v>
+        <v>0.005050702791589993</v>
       </c>
       <c r="S2">
         <v>0</v>
@@ -636,55 +639,55 @@
         <v>0</v>
       </c>
       <c r="U2">
-        <v>2611</v>
+        <v>1817.2</v>
       </c>
       <c r="V2">
-        <v>0.2405055129279773</v>
+        <v>0.1641123824833603</v>
       </c>
       <c r="W2">
-        <v>0.03220486111111111</v>
+        <v>0.1983678593848085</v>
       </c>
       <c r="X2">
-        <v>0.06678921138669867</v>
+        <v>0.08294173160657953</v>
       </c>
       <c r="Y2">
-        <v>-0.03458435027558757</v>
+        <v>0.115426127778229</v>
       </c>
       <c r="Z2">
-        <v>0.124273605719558</v>
+        <v>0.5250870733400845</v>
       </c>
       <c r="AA2">
-        <v>0</v>
+        <v>0.001456102893826261</v>
       </c>
       <c r="AB2">
-        <v>0.05768760607932769</v>
+        <v>0.07606120885174839</v>
       </c>
       <c r="AC2">
-        <v>-0.05768270582138359</v>
+        <v>-0.07343717216497109</v>
       </c>
       <c r="AD2">
-        <v>2989.8</v>
+        <v>3508.5</v>
       </c>
       <c r="AE2">
-        <v>181.5043965375471</v>
+        <v>178.2975756765998</v>
       </c>
       <c r="AF2">
-        <v>3171.304396537547</v>
+        <v>3686.7975756766</v>
       </c>
       <c r="AG2">
-        <v>560.3043965375473</v>
+        <v>1869.5975756766</v>
       </c>
       <c r="AH2">
-        <v>0.2260759789690337</v>
+        <v>0.249788151604969</v>
       </c>
       <c r="AI2">
-        <v>0.4624507646050217</v>
+        <v>0.4535588754828624</v>
       </c>
       <c r="AJ2">
-        <v>0.04907802504810254</v>
+        <v>0.1444541569156031</v>
       </c>
       <c r="AK2">
-        <v>0.1319417455024512</v>
+        <v>0.2962256066519742</v>
       </c>
       <c r="AL2">
         <v>0</v>
@@ -693,10 +696,10 @@
         <v>0</v>
       </c>
       <c r="AN2">
-        <v>81.26664854580049</v>
+        <v>80.23096272581752</v>
       </c>
       <c r="AP2">
-        <v>15.22980148240139</v>
+        <v>42.75320319406815</v>
       </c>
     </row>
     <row r="3">
@@ -707,7 +710,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>AU Small Finance Bank Limited (BSE:540611)</t>
+          <t>Dhanlaxmi Bank Limited (BSE:532180)</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -715,8 +718,11 @@
           <t>Banks (Regional)</t>
         </is>
       </c>
-      <c r="F3">
-        <v>0.109</v>
+      <c r="D3">
+        <v>0.0401</v>
+      </c>
+      <c r="E3">
+        <v>0.00342</v>
       </c>
       <c r="G3">
         <v>0</v>
@@ -725,16 +731,16 @@
         <v>0</v>
       </c>
       <c r="I3">
-        <v>0.002253105330134509</v>
+        <v>0.005493687814428856</v>
       </c>
       <c r="J3">
-        <v>0.001757930029608021</v>
+        <v>0.005088597702859859</v>
       </c>
       <c r="K3">
-        <v>152.3</v>
+        <v>1.83</v>
       </c>
       <c r="L3">
-        <v>0.3284451153763209</v>
+        <v>0.03512476007677543</v>
       </c>
       <c r="M3">
         <v>-0</v>
@@ -758,55 +764,46 @@
         <v>0</v>
       </c>
       <c r="U3">
-        <v>565.1</v>
+        <v>97.7</v>
       </c>
       <c r="V3">
-        <v>0.1294912923923006</v>
+        <v>1.614876033057851</v>
       </c>
       <c r="W3">
-        <v>0.2277894107089441</v>
+        <v>0.01552162849872774</v>
       </c>
       <c r="X3">
-        <v>0.06104835981820399</v>
+        <v>0.1039682105856551</v>
       </c>
       <c r="Y3">
-        <v>0.1667410508907401</v>
-      </c>
-      <c r="Z3">
-        <v>0.3083570597931132</v>
-      </c>
-      <c r="AA3">
-        <v>0.0005420701352519499</v>
+        <v>-0.08844658208692735</v>
       </c>
       <c r="AB3">
-        <v>0.05704801011558594</v>
-      </c>
-      <c r="AC3">
-        <v>-0.05650593998033399</v>
+        <v>0.07831028769932735</v>
       </c>
       <c r="AD3">
-        <v>669.8</v>
+        <v>71.3</v>
       </c>
       <c r="AE3">
-        <v>46.77617529208314</v>
+        <v>2.668894324341283</v>
       </c>
       <c r="AF3">
-        <v>716.5761752920831</v>
+        <v>73.96889432434128</v>
       </c>
       <c r="AG3">
-        <v>151.4761752920831</v>
+        <v>-23.73110567565872</v>
       </c>
       <c r="AH3">
-        <v>0.1410423051576206</v>
+        <v>0.5500818214949179</v>
       </c>
       <c r="AI3">
-        <v>0.4394080476210903</v>
+        <v>0.4036085588721585</v>
       </c>
       <c r="AJ3">
-        <v>0.0335460025502814</v>
+        <v>-0.6454125453521881</v>
       </c>
       <c r="AK3">
-        <v>0.1421409043423216</v>
+        <v>-0.2773333214486573</v>
       </c>
       <c r="AL3">
         <v>0</v>
@@ -815,10 +812,10 @@
         <v>0</v>
       </c>
       <c r="AN3">
-        <v>64.40384615384615</v>
+        <v>86.95121951219512</v>
       </c>
       <c r="AP3">
-        <v>14.56501685500799</v>
+        <v>-28.94037277519357</v>
       </c>
     </row>
     <row r="4">
@@ -829,7 +826,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>CSB Bank Limited (BSE:542867)</t>
+          <t>AU Small Finance Bank Limited (NSEI:AUBANK)</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -837,8 +834,8 @@
           <t>Banks (Regional)</t>
         </is>
       </c>
-      <c r="D4">
-        <v>0.285</v>
+      <c r="F4">
+        <v>0.242</v>
       </c>
       <c r="G4">
         <v>0</v>
@@ -847,94 +844,103 @@
         <v>0</v>
       </c>
       <c r="I4">
-        <v>0</v>
+        <v>0.003582374173100671</v>
       </c>
       <c r="J4">
-        <v>0</v>
+        <v>0.002813163881110019</v>
       </c>
       <c r="K4">
-        <v>37.1</v>
+        <v>154.7</v>
       </c>
       <c r="L4">
-        <v>0.2172131147540984</v>
+        <v>0.2748756218905473</v>
       </c>
       <c r="M4">
-        <v>-0</v>
+        <v>3.87</v>
       </c>
       <c r="N4">
-        <v>-0</v>
+        <v>0.0007342617538800136</v>
       </c>
       <c r="O4">
-        <v>-0</v>
+        <v>0.02501616031027796</v>
       </c>
       <c r="P4">
-        <v>-0</v>
+        <v>3.87</v>
       </c>
       <c r="Q4">
-        <v>-0</v>
+        <v>0.0007342617538800136</v>
       </c>
       <c r="R4">
-        <v>-0</v>
+        <v>0.02501616031027796</v>
       </c>
       <c r="S4">
         <v>0</v>
       </c>
+      <c r="T4">
+        <v>0</v>
+      </c>
       <c r="U4">
-        <v>327</v>
+        <v>485.2</v>
       </c>
       <c r="V4">
-        <v>0.596824237999635</v>
+        <v>0.09205783022805752</v>
       </c>
       <c r="W4">
-        <v>0.1309565831274268</v>
+        <v>0.169218989280245</v>
       </c>
       <c r="X4">
-        <v>0.06678921138669867</v>
+        <v>0.07807164672800188</v>
       </c>
       <c r="Y4">
-        <v>0.06416737174072808</v>
+        <v>0.09114734255224313</v>
       </c>
       <c r="Z4">
-        <v>0.3545775378866515</v>
+        <v>0.5176032948538041</v>
       </c>
       <c r="AA4">
-        <v>0</v>
+        <v>0.001456102893826261</v>
       </c>
       <c r="AB4">
-        <v>0.05684158468881476</v>
+        <v>0.07429126426095824</v>
       </c>
       <c r="AC4">
-        <v>-0.05684158468881476</v>
+        <v>-0.07283516136713197</v>
       </c>
       <c r="AD4">
-        <v>199</v>
+        <v>822.8</v>
       </c>
       <c r="AE4">
-        <v>0</v>
+        <v>68.41919907689471</v>
       </c>
       <c r="AF4">
-        <v>199</v>
+        <v>891.2191990768947</v>
       </c>
       <c r="AG4">
-        <v>-128</v>
+        <v>406.0191990768947</v>
       </c>
       <c r="AH4">
-        <v>0.2664345963315036</v>
+        <v>0.1446357269311648</v>
       </c>
       <c r="AI4">
-        <v>0.3844667697063369</v>
+        <v>0.4176051644455419</v>
       </c>
       <c r="AJ4">
-        <v>-0.3048344844010479</v>
+        <v>0.07152482575243371</v>
       </c>
       <c r="AK4">
-        <v>-0.6715634837355718</v>
+        <v>0.2462335324279044</v>
       </c>
       <c r="AL4">
         <v>0</v>
       </c>
       <c r="AM4">
         <v>0</v>
+      </c>
+      <c r="AN4">
+        <v>52.40764331210191</v>
+      </c>
+      <c r="AP4">
+        <v>25.86109548260476</v>
       </c>
     </row>
     <row r="5">
@@ -945,7 +951,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Bandhan Bank Limited (NSEI:BANDHANBNK)</t>
+          <t>CSB Bank Limited (NSEI:CSBBANK)</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -953,8 +959,8 @@
           <t>Banks (Regional)</t>
         </is>
       </c>
-      <c r="F5">
-        <v>0.139</v>
+      <c r="D5">
+        <v>0.362</v>
       </c>
       <c r="G5">
         <v>0</v>
@@ -963,91 +969,88 @@
         <v>0</v>
       </c>
       <c r="I5">
-        <v>0.0002216530455791597</v>
+        <v>0.001520446533304416</v>
       </c>
       <c r="J5">
-        <v>0.0002216530455791597</v>
+        <v>0.001135841854667128</v>
       </c>
       <c r="K5">
-        <v>-256.1</v>
+        <v>63.2</v>
       </c>
       <c r="L5">
-        <v>-3.027186761229315</v>
+        <v>0.3321071991592223</v>
       </c>
       <c r="M5">
-        <v>21.7</v>
+        <v>-0</v>
       </c>
       <c r="N5">
-        <v>0.003972394603401249</v>
+        <v>-0</v>
       </c>
       <c r="O5">
-        <v>-0.08473252635689182</v>
+        <v>-0</v>
       </c>
       <c r="P5">
-        <v>21.7</v>
+        <v>-0</v>
       </c>
       <c r="Q5">
-        <v>0.003972394603401249</v>
+        <v>-0</v>
       </c>
       <c r="R5">
-        <v>-0.08473252635689182</v>
+        <v>-0</v>
       </c>
       <c r="S5">
         <v>0</v>
       </c>
-      <c r="T5">
-        <v>0</v>
-      </c>
       <c r="U5">
-        <v>1404.9</v>
+        <v>200.4</v>
       </c>
       <c r="V5">
-        <v>0.2571805151298808</v>
+        <v>0.4020060180541625</v>
       </c>
       <c r="W5">
-        <v>-0.112978648314805</v>
+        <v>0.1983678593848085</v>
       </c>
       <c r="X5">
-        <v>0.06663356439653795</v>
+        <v>0.0821401864352613</v>
       </c>
       <c r="Y5">
-        <v>-0.179612212711343</v>
+        <v>0.1162276729495472</v>
       </c>
       <c r="Z5">
-        <v>0.02210778530602862</v>
+        <v>0.9947554739038194</v>
       </c>
       <c r="AA5">
-        <v>4.90025794409144e-06</v>
+        <v>0.001129884902419192</v>
       </c>
       <c r="AB5">
-        <v>0.05768760607932769</v>
+        <v>0.07456705706739028</v>
       </c>
       <c r="AC5">
-        <v>-0.05768270582138359</v>
+        <v>-0.07343717216497109</v>
       </c>
       <c r="AD5">
-        <v>1874.7</v>
+        <v>166.1</v>
       </c>
       <c r="AE5">
-        <v>79.90624076172001</v>
+        <v>0.7032951235608484</v>
       </c>
       <c r="AF5">
-        <v>1954.60624076172</v>
+        <v>166.8032951235608</v>
       </c>
       <c r="AG5">
-        <v>549.70624076172</v>
+        <v>-33.59670487643916</v>
       </c>
       <c r="AH5">
-        <v>0.2635196899408311</v>
+        <v>0.2507176746999005</v>
       </c>
       <c r="AI5">
-        <v>0.4979626854925238</v>
+        <v>0.3196670022638752</v>
       </c>
       <c r="AJ5">
-        <v>0.09142865913399706</v>
+        <v>-0.07226600720803648</v>
       </c>
       <c r="AK5">
-        <v>0.2181108913953173</v>
+        <v>-0.1045313019069179</v>
       </c>
       <c r="AL5">
         <v>0</v>
@@ -1056,10 +1059,10 @@
         <v>0</v>
       </c>
       <c r="AN5">
-        <v>117.16875</v>
+        <v>386.2790697674419</v>
       </c>
       <c r="AP5">
-        <v>34.3566400476075</v>
+        <v>-78.13187180567247</v>
       </c>
     </row>
     <row r="6">
@@ -1070,7 +1073,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Ujjivan Small Finance Bank Limited (BSE:542904)</t>
+          <t>Ujjivan Small Finance Bank Limited (NSEI:UJJIVANSFB)</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -1085,16 +1088,16 @@
         <v>0</v>
       </c>
       <c r="I6">
-        <v>-0.01284460366349026</v>
+        <v>0.005190121703373626</v>
       </c>
       <c r="J6">
-        <v>-0.01284460366349026</v>
+        <v>0.003859321266611158</v>
       </c>
       <c r="K6">
-        <v>-87.59999999999999</v>
+        <v>72.5</v>
       </c>
       <c r="L6">
-        <v>-1.457570715474209</v>
+        <v>0.2384084182834594</v>
       </c>
       <c r="M6">
         <v>-0</v>
@@ -1103,7 +1106,7 @@
         <v>-0</v>
       </c>
       <c r="O6">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="P6">
         <v>-0</v>
@@ -1112,61 +1115,61 @@
         <v>-0</v>
       </c>
       <c r="R6">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="S6">
         <v>0</v>
       </c>
       <c r="U6">
-        <v>168</v>
+        <v>196.7</v>
       </c>
       <c r="V6">
-        <v>0.3894297635605007</v>
+        <v>0.2871952109797051</v>
       </c>
       <c r="W6">
-        <v>-0.192063144047358</v>
+        <v>0.1986301369863014</v>
       </c>
       <c r="X6">
-        <v>0.07489549200685347</v>
+        <v>0.08294173160657953</v>
       </c>
       <c r="Y6">
-        <v>-0.2669586360542115</v>
+        <v>0.1156884053797218</v>
       </c>
       <c r="Z6">
-        <v>0.06377944894884233</v>
+        <v>0.6587834772011432</v>
       </c>
       <c r="AA6">
-        <v>-0.0008192217436236902</v>
+        <v>0.002542457083654419</v>
       </c>
       <c r="AB6">
-        <v>0.05835752218413159</v>
+        <v>0.07606120885174839</v>
       </c>
       <c r="AC6">
-        <v>-0.05917674392775528</v>
+        <v>-0.07351875176809397</v>
       </c>
       <c r="AD6">
-        <v>226.1</v>
+        <v>213</v>
       </c>
       <c r="AE6">
-        <v>51.80980340087882</v>
+        <v>38.5084199500204</v>
       </c>
       <c r="AF6">
-        <v>277.9098034008788</v>
+        <v>251.5084199500204</v>
       </c>
       <c r="AG6">
-        <v>109.9098034008788</v>
+        <v>54.80841995002041</v>
       </c>
       <c r="AH6">
-        <v>0.3918031332266999</v>
+        <v>0.2685883793777125</v>
       </c>
       <c r="AI6">
-        <v>0.4322687287249086</v>
+        <v>0.3519035356650876</v>
       </c>
       <c r="AJ6">
-        <v>0.2030441767548826</v>
+        <v>0.07409462765575067</v>
       </c>
       <c r="AK6">
-        <v>0.2314330060441018</v>
+        <v>0.1058060406726758</v>
       </c>
       <c r="AL6">
         <v>0</v>
@@ -1175,10 +1178,10 @@
         <v>0</v>
       </c>
       <c r="AN6">
-        <v>23.57664233576642</v>
+        <v>22.95258620689655</v>
       </c>
       <c r="AP6">
-        <v>11.46087626703637</v>
+        <v>5.906079735993579</v>
       </c>
     </row>
     <row r="7">
@@ -1189,7 +1192,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Dhanlaxmi Bank Limited (BSE:532180)</t>
+          <t>Bandhan Bank Limited (NSEI:BANDHANBNK)</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -1197,9 +1200,6 @@
           <t>Banks (Regional)</t>
         </is>
       </c>
-      <c r="D7">
-        <v>0.144</v>
-      </c>
       <c r="G7">
         <v>0</v>
       </c>
@@ -1207,16 +1207,16 @@
         <v>0</v>
       </c>
       <c r="I7">
-        <v>0.003337239584915002</v>
+        <v>0.003477573608811964</v>
       </c>
       <c r="J7">
-        <v>0.002787532480253722</v>
+        <v>0.002623539536172005</v>
       </c>
       <c r="K7">
-        <v>3.71</v>
+        <v>474</v>
       </c>
       <c r="L7">
-        <v>0.06266891891891892</v>
+        <v>0.4226105563480742</v>
       </c>
       <c r="M7">
         <v>-0</v>
@@ -1240,55 +1240,55 @@
         <v>0</v>
       </c>
       <c r="U7">
-        <v>146</v>
+        <v>837.2</v>
       </c>
       <c r="V7">
-        <v>2.90258449304175</v>
+        <v>0.1836609336609337</v>
       </c>
       <c r="W7">
-        <v>0.03220486111111111</v>
+        <v>0.2405358773977469</v>
       </c>
       <c r="X7">
-        <v>0.06962409905436598</v>
+        <v>0.08633551717946565</v>
       </c>
       <c r="Y7">
-        <v>-0.03741923794325487</v>
+        <v>0.1542003602182813</v>
       </c>
       <c r="Z7">
-        <v>-7.319645917887134</v>
+        <v>0.4471380156151188</v>
       </c>
       <c r="AA7">
-        <v>-0.02040375074006695</v>
+        <v>0.00117308426209176</v>
       </c>
       <c r="AB7">
-        <v>0.05796041112258402</v>
+        <v>0.07659721507610676</v>
       </c>
       <c r="AC7">
-        <v>-0.07836416186265098</v>
+        <v>-0.075424130814015</v>
       </c>
       <c r="AD7">
-        <v>20.2</v>
+        <v>2235.3</v>
       </c>
       <c r="AE7">
-        <v>3.01217708286516</v>
+        <v>67.99776720178251</v>
       </c>
       <c r="AF7">
-        <v>23.21217708286516</v>
+        <v>2303.297767201783</v>
       </c>
       <c r="AG7">
-        <v>-122.7878229171348</v>
+        <v>1466.097767201783</v>
       </c>
       <c r="AH7">
-        <v>0.3157596197525165</v>
+        <v>0.3356746165958099</v>
       </c>
       <c r="AI7">
-        <v>0.1644945004939885</v>
+        <v>0.5034863250891101</v>
       </c>
       <c r="AJ7">
-        <v>1.693909652349484</v>
+        <v>0.2433560147010804</v>
       </c>
       <c r="AK7">
-        <v>25.12116846268877</v>
+        <v>0.392267195466295</v>
       </c>
       <c r="AL7">
         <v>0</v>
@@ -1297,10 +1297,10 @@
         <v>0</v>
       </c>
       <c r="AN7">
-        <v>25.25</v>
+        <v>127.7314285714286</v>
       </c>
       <c r="AP7">
-        <v>-153.4847786464185</v>
+        <v>83.7770152686733</v>
       </c>
     </row>
   </sheetData>

--- a/research/traditional_assets/database/data/india/india_banks_regional.xlsx
+++ b/research/traditional_assets/database/data/india/india_banks_regional.xlsx
@@ -588,13 +588,13 @@
         </is>
       </c>
       <c r="D2">
-        <v>0.20105</v>
+        <v>0.293</v>
       </c>
       <c r="E2">
-        <v>0.00342</v>
+        <v>0.3720000000000001</v>
       </c>
       <c r="F2">
-        <v>0.242</v>
+        <v>0.373</v>
       </c>
       <c r="G2">
         <v>0</v>
@@ -603,34 +603,34 @@
         <v>0</v>
       </c>
       <c r="I2">
-        <v>0.0036175914943207</v>
+        <v>0.005055325837455069</v>
       </c>
       <c r="J2">
-        <v>0.002862667548699841</v>
+        <v>0.004066334574788487</v>
       </c>
       <c r="K2">
-        <v>766.23</v>
+        <v>733</v>
       </c>
       <c r="L2">
-        <v>0.3434622797973912</v>
+        <v>0.2941766665328892</v>
       </c>
       <c r="M2">
-        <v>3.87</v>
+        <v>66.53</v>
       </c>
       <c r="N2">
-        <v>0.0003495019371618998</v>
+        <v>0.004985873483366683</v>
       </c>
       <c r="O2">
-        <v>0.005050702791589993</v>
+        <v>0.09076398362892224</v>
       </c>
       <c r="P2">
-        <v>3.87</v>
+        <v>66.53</v>
       </c>
       <c r="Q2">
-        <v>0.0003495019371618998</v>
+        <v>0.004985873483366683</v>
       </c>
       <c r="R2">
-        <v>0.005050702791589993</v>
+        <v>0.09076398362892224</v>
       </c>
       <c r="S2">
         <v>0</v>
@@ -639,55 +639,55 @@
         <v>0</v>
       </c>
       <c r="U2">
-        <v>1817.2</v>
+        <v>2200.3</v>
       </c>
       <c r="V2">
-        <v>0.1641123824833603</v>
+        <v>0.1648942946858818</v>
       </c>
       <c r="W2">
-        <v>0.1983678593848085</v>
+        <v>0.1555233727572612</v>
       </c>
       <c r="X2">
-        <v>0.08294173160657953</v>
+        <v>0.06681267007572513</v>
       </c>
       <c r="Y2">
-        <v>0.115426127778229</v>
+        <v>0.08871070268153612</v>
       </c>
       <c r="Z2">
-        <v>0.5250870733400845</v>
+        <v>0.3940534898895816</v>
       </c>
       <c r="AA2">
-        <v>0.001456102893826261</v>
+        <v>0.001746726649554409</v>
       </c>
       <c r="AB2">
-        <v>0.07606120885174839</v>
+        <v>0.0624593705913936</v>
       </c>
       <c r="AC2">
-        <v>-0.07343717216497109</v>
+        <v>-0.06019242226195707</v>
       </c>
       <c r="AD2">
-        <v>3508.5</v>
+        <v>3284</v>
       </c>
       <c r="AE2">
-        <v>178.2975756765998</v>
+        <v>190.153223054066</v>
       </c>
       <c r="AF2">
-        <v>3686.7975756766</v>
+        <v>3474.153223054066</v>
       </c>
       <c r="AG2">
-        <v>1869.5975756766</v>
+        <v>1273.853223054066</v>
       </c>
       <c r="AH2">
-        <v>0.249788151604969</v>
+        <v>0.2065753088088357</v>
       </c>
       <c r="AI2">
-        <v>0.4535588754828624</v>
+        <v>0.4083274359583537</v>
       </c>
       <c r="AJ2">
-        <v>0.1444541569156031</v>
+        <v>0.08714544791566137</v>
       </c>
       <c r="AK2">
-        <v>0.2962256066519742</v>
+        <v>0.2019439869018743</v>
       </c>
       <c r="AL2">
         <v>0</v>
@@ -696,10 +696,10 @@
         <v>0</v>
       </c>
       <c r="AN2">
-        <v>80.23096272581752</v>
+        <v>64.86657317241789</v>
       </c>
       <c r="AP2">
-        <v>42.75320319406815</v>
+        <v>25.16153876496861</v>
       </c>
     </row>
     <row r="3">
@@ -719,10 +719,7 @@
         </is>
       </c>
       <c r="D3">
-        <v>0.0401</v>
-      </c>
-      <c r="E3">
-        <v>0.00342</v>
+        <v>0.212</v>
       </c>
       <c r="G3">
         <v>0</v>
@@ -731,16 +728,16 @@
         <v>0</v>
       </c>
       <c r="I3">
-        <v>0.005493687814428856</v>
+        <v>0.01919989518066276</v>
       </c>
       <c r="J3">
-        <v>0.005088597702859859</v>
+        <v>0.01919989518066276</v>
       </c>
       <c r="K3">
-        <v>1.83</v>
+        <v>13.4</v>
       </c>
       <c r="L3">
-        <v>0.03512476007677543</v>
+        <v>0.2005988023952096</v>
       </c>
       <c r="M3">
         <v>-0</v>
@@ -764,46 +761,55 @@
         <v>0</v>
       </c>
       <c r="U3">
-        <v>97.7</v>
+        <v>110</v>
       </c>
       <c r="V3">
-        <v>1.614876033057851</v>
+        <v>1.170212765957447</v>
       </c>
       <c r="W3">
-        <v>0.01552162849872774</v>
+        <v>0.1225983531564501</v>
       </c>
       <c r="X3">
-        <v>0.1039682105856551</v>
+        <v>0.06681267007572513</v>
       </c>
       <c r="Y3">
-        <v>-0.08844658208692735</v>
+        <v>0.05578568308072501</v>
+      </c>
+      <c r="Z3">
+        <v>0.7168363777836776</v>
+      </c>
+      <c r="AA3">
+        <v>0.01376318331513258</v>
       </c>
       <c r="AB3">
-        <v>0.07831028769932735</v>
+        <v>0.06329942814367935</v>
+      </c>
+      <c r="AC3">
+        <v>-0.04953624482854677</v>
       </c>
       <c r="AD3">
-        <v>71.3</v>
+        <v>19.9</v>
       </c>
       <c r="AE3">
-        <v>2.668894324341283</v>
+        <v>10.28723500965864</v>
       </c>
       <c r="AF3">
-        <v>73.96889432434128</v>
+        <v>30.18723500965864</v>
       </c>
       <c r="AG3">
-        <v>-23.73110567565872</v>
+        <v>-79.81276499034136</v>
       </c>
       <c r="AH3">
-        <v>0.5500818214949179</v>
+        <v>0.2430784050173178</v>
       </c>
       <c r="AI3">
-        <v>0.4036085588721585</v>
+        <v>0.1968040887350097</v>
       </c>
       <c r="AJ3">
-        <v>-0.6454125453521881</v>
+        <v>-5.625674413372657</v>
       </c>
       <c r="AK3">
-        <v>-0.2773333214486573</v>
+        <v>-1.839544856282588</v>
       </c>
       <c r="AL3">
         <v>0</v>
@@ -812,10 +818,10 @@
         <v>0</v>
       </c>
       <c r="AN3">
-        <v>86.95121951219512</v>
+        <v>5.958083832335329</v>
       </c>
       <c r="AP3">
-        <v>-28.94037277519357</v>
+        <v>-23.89603742225789</v>
       </c>
     </row>
     <row r="4">
@@ -826,7 +832,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>AU Small Finance Bank Limited (NSEI:AUBANK)</t>
+          <t>Ujjivan Small Finance Bank Limited (NSEI:UJJIVANSFB)</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -834,8 +840,11 @@
           <t>Banks (Regional)</t>
         </is>
       </c>
-      <c r="F4">
-        <v>0.242</v>
+      <c r="D4">
+        <v>0.293</v>
+      </c>
+      <c r="E4">
+        <v>0.466</v>
       </c>
       <c r="G4">
         <v>0</v>
@@ -844,34 +853,34 @@
         <v>0</v>
       </c>
       <c r="I4">
-        <v>0.003582374173100671</v>
+        <v>0.006357888944466695</v>
       </c>
       <c r="J4">
-        <v>0.002813163881110019</v>
+        <v>0.004776324530420254</v>
       </c>
       <c r="K4">
-        <v>154.7</v>
+        <v>151</v>
       </c>
       <c r="L4">
-        <v>0.2748756218905473</v>
+        <v>0.3424036281179138</v>
       </c>
       <c r="M4">
-        <v>3.87</v>
+        <v>29.4</v>
       </c>
       <c r="N4">
-        <v>0.0007342617538800136</v>
+        <v>0.0219435736677116</v>
       </c>
       <c r="O4">
-        <v>0.02501616031027796</v>
+        <v>0.1947019867549669</v>
       </c>
       <c r="P4">
-        <v>3.87</v>
+        <v>29.4</v>
       </c>
       <c r="Q4">
-        <v>0.0007342617538800136</v>
+        <v>0.0219435736677116</v>
       </c>
       <c r="R4">
-        <v>0.02501616031027796</v>
+        <v>0.1947019867549669</v>
       </c>
       <c r="S4">
         <v>0</v>
@@ -880,55 +889,55 @@
         <v>0</v>
       </c>
       <c r="U4">
-        <v>485.2</v>
+        <v>222.3</v>
       </c>
       <c r="V4">
-        <v>0.09205783022805752</v>
+        <v>0.1659202866099418</v>
       </c>
       <c r="W4">
-        <v>0.169218989280245</v>
+        <v>0.325993091537133</v>
       </c>
       <c r="X4">
-        <v>0.07807164672800188</v>
+        <v>0.06749995957006003</v>
       </c>
       <c r="Y4">
-        <v>0.09114734255224313</v>
+        <v>0.258493131967073</v>
       </c>
       <c r="Z4">
-        <v>0.5176032948538041</v>
+        <v>0.8513828182015263</v>
       </c>
       <c r="AA4">
-        <v>0.001456102893826261</v>
+        <v>0.004066480639354277</v>
       </c>
       <c r="AB4">
-        <v>0.07429126426095824</v>
+        <v>0.06345898758224532</v>
       </c>
       <c r="AC4">
-        <v>-0.07283516136713197</v>
+        <v>-0.05939250694289104</v>
       </c>
       <c r="AD4">
-        <v>822.8</v>
+        <v>449.3</v>
       </c>
       <c r="AE4">
-        <v>68.41919907689471</v>
+        <v>38.48085487745094</v>
       </c>
       <c r="AF4">
-        <v>891.2191990768947</v>
+        <v>487.780854877451</v>
       </c>
       <c r="AG4">
-        <v>406.0191990768947</v>
+        <v>265.480854877451</v>
       </c>
       <c r="AH4">
-        <v>0.1446357269311648</v>
+        <v>0.2668997399352596</v>
       </c>
       <c r="AI4">
-        <v>0.4176051644455419</v>
+        <v>0.459312286692531</v>
       </c>
       <c r="AJ4">
-        <v>0.07152482575243371</v>
+        <v>0.1653796929495668</v>
       </c>
       <c r="AK4">
-        <v>0.2462335324279044</v>
+        <v>0.3161687602323589</v>
       </c>
       <c r="AL4">
         <v>0</v>
@@ -937,10 +946,10 @@
         <v>0</v>
       </c>
       <c r="AN4">
-        <v>52.40764331210191</v>
+        <v>42.79047619047619</v>
       </c>
       <c r="AP4">
-        <v>25.86109548260476</v>
+        <v>25.28389094070961</v>
       </c>
     </row>
     <row r="5">
@@ -951,7 +960,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>CSB Bank Limited (NSEI:CSBBANK)</t>
+          <t>AU Small Finance Bank Limited (NSEI:AUBANK)</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -960,7 +969,13 @@
         </is>
       </c>
       <c r="D5">
-        <v>0.362</v>
+        <v>0.324</v>
+      </c>
+      <c r="E5">
+        <v>0.3720000000000001</v>
+      </c>
+      <c r="F5">
+        <v>0.277</v>
       </c>
       <c r="G5">
         <v>0</v>
@@ -969,88 +984,91 @@
         <v>0</v>
       </c>
       <c r="I5">
-        <v>0.001520446533304416</v>
+        <v>0.005221263482030839</v>
       </c>
       <c r="J5">
-        <v>0.001135841854667128</v>
+        <v>0.003993946304220662</v>
       </c>
       <c r="K5">
-        <v>63.2</v>
+        <v>193.3</v>
       </c>
       <c r="L5">
-        <v>0.3321071991592223</v>
+        <v>0.2672842920353982</v>
       </c>
       <c r="M5">
-        <v>-0</v>
+        <v>8.029999999999999</v>
       </c>
       <c r="N5">
-        <v>-0</v>
+        <v>0.001271535343298708</v>
       </c>
       <c r="O5">
-        <v>-0</v>
+        <v>0.04154164511122607</v>
       </c>
       <c r="P5">
-        <v>-0</v>
+        <v>8.029999999999999</v>
       </c>
       <c r="Q5">
-        <v>-0</v>
+        <v>0.001271535343298708</v>
       </c>
       <c r="R5">
-        <v>-0</v>
+        <v>0.04154164511122607</v>
       </c>
       <c r="S5">
         <v>0</v>
       </c>
+      <c r="T5">
+        <v>0</v>
+      </c>
       <c r="U5">
-        <v>200.4</v>
+        <v>753.1</v>
       </c>
       <c r="V5">
-        <v>0.4020060180541625</v>
+        <v>0.1192519635165949</v>
       </c>
       <c r="W5">
-        <v>0.1983678593848085</v>
+        <v>0.1555233727572612</v>
       </c>
       <c r="X5">
-        <v>0.0821401864352613</v>
+        <v>0.06348721310726067</v>
       </c>
       <c r="Y5">
-        <v>0.1162276729495472</v>
+        <v>0.09203615965000057</v>
       </c>
       <c r="Z5">
-        <v>0.9947554739038194</v>
+        <v>0.4373435485871529</v>
       </c>
       <c r="AA5">
-        <v>0.001129884902419192</v>
+        <v>0.001746726649554409</v>
       </c>
       <c r="AB5">
-        <v>0.07456705706739028</v>
+        <v>0.06193914891151148</v>
       </c>
       <c r="AC5">
-        <v>-0.07343717216497109</v>
+        <v>-0.06019242226195707</v>
       </c>
       <c r="AD5">
-        <v>166.1</v>
+        <v>643.2</v>
       </c>
       <c r="AE5">
-        <v>0.7032951235608484</v>
+        <v>73.11991124897648</v>
       </c>
       <c r="AF5">
-        <v>166.8032951235608</v>
+        <v>716.3199112489765</v>
       </c>
       <c r="AG5">
-        <v>-33.59670487643916</v>
+        <v>-36.78008875102353</v>
       </c>
       <c r="AH5">
-        <v>0.2507176746999005</v>
+        <v>0.1018726989740885</v>
       </c>
       <c r="AI5">
-        <v>0.3196670022638752</v>
+        <v>0.3359660530675138</v>
       </c>
       <c r="AJ5">
-        <v>-0.07226600720803648</v>
+        <v>-0.005858175985509514</v>
       </c>
       <c r="AK5">
-        <v>-0.1045313019069179</v>
+        <v>-0.02667118034409804</v>
       </c>
       <c r="AL5">
         <v>0</v>
@@ -1059,10 +1077,10 @@
         <v>0</v>
       </c>
       <c r="AN5">
-        <v>386.2790697674419</v>
+        <v>34.95652173913044</v>
       </c>
       <c r="AP5">
-        <v>-78.13187180567247</v>
+        <v>-1.998917866903453</v>
       </c>
     </row>
     <row r="6">
@@ -1073,7 +1091,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Ujjivan Small Finance Bank Limited (NSEI:UJJIVANSFB)</t>
+          <t>Bandhan Bank Limited (NSEI:BANDHANBNK)</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -1081,6 +1099,15 @@
           <t>Banks (Regional)</t>
         </is>
       </c>
+      <c r="D6">
+        <v>0.16</v>
+      </c>
+      <c r="E6">
+        <v>0.0892</v>
+      </c>
+      <c r="F6">
+        <v>0.469</v>
+      </c>
       <c r="G6">
         <v>0</v>
       </c>
@@ -1088,88 +1115,91 @@
         <v>0</v>
       </c>
       <c r="I6">
-        <v>0.005190121703373626</v>
+        <v>0.004349614194171277</v>
       </c>
       <c r="J6">
-        <v>0.003859321266611158</v>
+        <v>0.003300786360697082</v>
       </c>
       <c r="K6">
-        <v>72.5</v>
+        <v>305.8</v>
       </c>
       <c r="L6">
-        <v>0.2384084182834594</v>
+        <v>0.2968355659095321</v>
       </c>
       <c r="M6">
-        <v>-0</v>
+        <v>29.1</v>
       </c>
       <c r="N6">
-        <v>-0</v>
+        <v>0.006159773083273359</v>
       </c>
       <c r="O6">
-        <v>-0</v>
+        <v>0.09516023544800524</v>
       </c>
       <c r="P6">
-        <v>-0</v>
+        <v>29.1</v>
       </c>
       <c r="Q6">
-        <v>-0</v>
+        <v>0.006159773083273359</v>
       </c>
       <c r="R6">
-        <v>-0</v>
+        <v>0.09516023544800524</v>
       </c>
       <c r="S6">
         <v>0</v>
       </c>
+      <c r="T6">
+        <v>0</v>
+      </c>
       <c r="U6">
-        <v>196.7</v>
+        <v>922.9</v>
       </c>
       <c r="V6">
-        <v>0.2871952109797051</v>
+        <v>0.1953558274416833</v>
       </c>
       <c r="W6">
-        <v>0.1986301369863014</v>
+        <v>0.1346306242845822</v>
       </c>
       <c r="X6">
-        <v>0.08294173160657953</v>
+        <v>0.06852258283943009</v>
       </c>
       <c r="Y6">
-        <v>0.1156884053797218</v>
+        <v>0.0661080414451521</v>
       </c>
       <c r="Z6">
-        <v>0.6587834772011432</v>
+        <v>0.2756686576484144</v>
       </c>
       <c r="AA6">
-        <v>0.002542457083654419</v>
+        <v>0.0009099233452375593</v>
       </c>
       <c r="AB6">
-        <v>0.07606120885174839</v>
+        <v>0.0624593705913936</v>
       </c>
       <c r="AC6">
-        <v>-0.07351875176809397</v>
+        <v>-0.06154944724615604</v>
       </c>
       <c r="AD6">
-        <v>213</v>
+        <v>1954.1</v>
       </c>
       <c r="AE6">
-        <v>38.5084199500204</v>
+        <v>67.59513728582375</v>
       </c>
       <c r="AF6">
-        <v>251.5084199500204</v>
+        <v>2021.695137285824</v>
       </c>
       <c r="AG6">
-        <v>54.80841995002041</v>
+        <v>1098.795137285824</v>
       </c>
       <c r="AH6">
-        <v>0.2685883793777125</v>
+        <v>0.2996926421390004</v>
       </c>
       <c r="AI6">
-        <v>0.3519035356650876</v>
+        <v>0.4468234341290879</v>
       </c>
       <c r="AJ6">
-        <v>0.07409462765575067</v>
+        <v>0.1886993053196996</v>
       </c>
       <c r="AK6">
-        <v>0.1058060406726758</v>
+        <v>0.3050772193100877</v>
       </c>
       <c r="AL6">
         <v>0</v>
@@ -1178,10 +1208,10 @@
         <v>0</v>
       </c>
       <c r="AN6">
-        <v>22.95258620689655</v>
+        <v>108.5611111111111</v>
       </c>
       <c r="AP6">
-        <v>5.906079735993579</v>
+        <v>61.04417429365688</v>
       </c>
     </row>
     <row r="7">
@@ -1192,7 +1222,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Bandhan Bank Limited (NSEI:BANDHANBNK)</t>
+          <t>CSB Bank Limited (NSEI:CSBBANK)</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -1200,6 +1230,9 @@
           <t>Banks (Regional)</t>
         </is>
       </c>
+      <c r="D7">
+        <v>0.441</v>
+      </c>
       <c r="G7">
         <v>0</v>
       </c>
@@ -1207,16 +1240,16 @@
         <v>0</v>
       </c>
       <c r="I7">
-        <v>0.003477573608811964</v>
+        <v>0.001097540449322168</v>
       </c>
       <c r="J7">
-        <v>0.002623539536172005</v>
+        <v>0.0008196224814680564</v>
       </c>
       <c r="K7">
-        <v>474</v>
+        <v>69.5</v>
       </c>
       <c r="L7">
-        <v>0.4226105563480742</v>
+        <v>0.3015184381778742</v>
       </c>
       <c r="M7">
         <v>-0</v>
@@ -1240,55 +1273,55 @@
         <v>0</v>
       </c>
       <c r="U7">
-        <v>837.2</v>
+        <v>192</v>
       </c>
       <c r="V7">
-        <v>0.1836609336609337</v>
+        <v>0.2205628948879954</v>
       </c>
       <c r="W7">
-        <v>0.2405358773977469</v>
+        <v>0.1957746478873239</v>
       </c>
       <c r="X7">
-        <v>0.08633551717946565</v>
+        <v>0.06568373992272958</v>
       </c>
       <c r="Y7">
-        <v>0.1542003602182813</v>
+        <v>0.1300909079645944</v>
       </c>
       <c r="Z7">
-        <v>0.4471380156151188</v>
+        <v>0.7172416196231608</v>
       </c>
       <c r="AA7">
-        <v>0.00117308426209176</v>
+        <v>0.0005878673560877029</v>
       </c>
       <c r="AB7">
-        <v>0.07659721507610676</v>
+        <v>0.06219825486305247</v>
       </c>
       <c r="AC7">
-        <v>-0.075424130814015</v>
+        <v>-0.06161038750696477</v>
       </c>
       <c r="AD7">
-        <v>2235.3</v>
+        <v>217.5</v>
       </c>
       <c r="AE7">
-        <v>67.99776720178251</v>
+        <v>0.6700846321562021</v>
       </c>
       <c r="AF7">
-        <v>2303.297767201783</v>
+        <v>218.1700846321562</v>
       </c>
       <c r="AG7">
-        <v>1466.097767201783</v>
+        <v>26.1700846321562</v>
       </c>
       <c r="AH7">
-        <v>0.3356746165958099</v>
+        <v>0.2004005508297514</v>
       </c>
       <c r="AI7">
-        <v>0.5034863250891101</v>
+        <v>0.3429430114720117</v>
       </c>
       <c r="AJ7">
-        <v>0.2433560147010804</v>
+        <v>0.02918585673892761</v>
       </c>
       <c r="AK7">
-        <v>0.392267195466295</v>
+        <v>0.05891906172345942</v>
       </c>
       <c r="AL7">
         <v>0</v>
@@ -1297,10 +1330,10 @@
         <v>0</v>
       </c>
       <c r="AN7">
-        <v>127.7314285714286</v>
+        <v>562.015503875969</v>
       </c>
       <c r="AP7">
-        <v>83.7770152686733</v>
+        <v>67.62295770582999</v>
       </c>
     </row>
   </sheetData>
